--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:52</t>
+    <t xml:space="preserve">2026-09-10 01:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:02</t>
+    <t xml:space="preserve">2026-09-18 11:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:09</t>
+    <t xml:space="preserve">2026-09-23 14:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -540,7 +540,9 @@
       <c r="C5" s="2" t="n">
         <v>15201</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E5" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:33</t>
+    <t xml:space="preserve">2026-10-02 15:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:56</t>
+    <t xml:space="preserve">2026-10-05 15:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
